--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_146_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_146_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0337</v>
+        <v>8.5687</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1322</v>
+        <v>5.4991</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9015</v>
+        <v>3.0695</v>
       </c>
       <c r="G2" t="n">
         <v>4.723</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1303</v>
+        <v>0.6653</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0657</v>
+        <v>0.4327</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0646</v>
+        <v>0.2326</v>
       </c>
       <c r="V2" t="n">
         <v>1.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1081</v>
+        <v>5.3521</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2454</v>
+        <v>3.7919</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8627</v>
+        <v>1.5603</v>
       </c>
       <c r="G3" t="n">
         <v>5.9653</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1401</v>
+        <v>0.3842</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6563</v>
+        <v>-0.1098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7965</v>
+        <v>0.494</v>
       </c>
       <c r="V3" t="n">
         <v>0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4944</v>
+        <v>2.4842</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1164</v>
+        <v>5.4087</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.622</v>
+        <v>-2.9245</v>
       </c>
       <c r="G4" t="n">
         <v>3.214</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8913</v>
+        <v>-0.1188</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6018</v>
+        <v>-0.1059</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2895</v>
+        <v>-0.013</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0026</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.063</v>
+        <v>2.4072</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0049</v>
+        <v>1.3155</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0581</v>
+        <v>1.0917</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8253</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6067</v>
+        <v>-0.2625</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>-0.4283</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1322</v>
+        <v>0.1658</v>
       </c>
       <c r="V5" t="n">
         <v>1.6393</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8771</v>
+        <v>0.9271</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2463</v>
+        <v>1.1284</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3693</v>
+        <v>-0.2012</v>
       </c>
       <c r="G6" t="n">
         <v>0.1948</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4775</v>
+        <v>-0.4274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0351</v>
+        <v>-0.1531</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4424</v>
+        <v>-0.2743</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8225</v>
+        <v>0.7358</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0112</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8336</v>
+        <v>0.1506</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1908</v>
+        <v>-0.7945</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5293</v>
+        <v>-1.119</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3384</v>
+        <v>0.3245</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1333</v>
+        <v>0.471</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6351</v>
+        <v>-0.2248</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5018</v>
+        <v>0.6958</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0576</v>
+        <v>-1.2655</v>
       </c>
       <c r="N7" t="n">
         <v>-0.8942</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8366</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3062</v>
+        <v>0.3705</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1221</v>
+        <v>0.1142</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4283</v>
+        <v>0.2563</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4931</v>
+        <v>0.6874</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5105</v>
+        <v>-0.2471</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0174</v>
+        <v>0.9344</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7945</v>
+        <v>-0.1908</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.119</v>
+        <v>-1.5293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3245</v>
+        <v>1.3384</v>
       </c>
       <c r="J8" t="n">
-        <v>0.471</v>
+        <v>-0.1333</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2248</v>
+        <v>-0.6351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6958</v>
+        <v>0.5018</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2655</v>
+        <v>-0.0576</v>
       </c>
       <c r="N8" t="n">
         <v>-0.8942</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3713</v>
+        <v>0.8366</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1278</v>
+        <v>-0.4413</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0395</v>
+        <v>-0.1138</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0883</v>
+        <v>-0.3275</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1134</v>
+        <v>-0.029</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1692</v>
+        <v>0.2872</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2826</v>
+        <v>-0.3162</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3155</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2464</v>
+        <v>-0.1621</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0272</v>
+        <v>0.0907</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2192</v>
+        <v>-0.2528</v>
       </c>
       <c r="V9" t="n">
         <v>2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0271</v>
+        <v>-1.3701</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1368</v>
+        <v>-0.547</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8903</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3889</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7257</v>
+        <v>-0.0688</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0781</v>
+        <v>-1.7339</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9631</v>
+        <v>-2.6525</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8851</v>
+        <v>0.9187</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8581</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0602</v>
+        <v>0.284</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4323</v>
+        <v>-0.1217</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.155</v>
+        <v>-2.0206</v>
       </c>
       <c r="E12" t="n">
         <v>-1.353</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8021</v>
+        <v>-0.6676</v>
       </c>
       <c r="G12" t="n">
         <v>0.7579</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.449</v>
+        <v>-0.3145</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7525</v>
+        <v>-3.8698</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9338</v>
+        <v>-2.8158</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8187</v>
+        <v>-1.054</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8014</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2087</v>
+        <v>0.0914</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4327</v>
+        <v>0.1975</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.7658</v>
+        <v>12.1391</v>
       </c>
       <c r="E14" t="n">
-        <v>10.027</v>
+        <v>10.4006</v>
       </c>
       <c r="F14" t="n">
         <v>1.7386</v>
@@ -1537,7 +1537,7 @@
         <v>-2.408099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.638999999999999</v>
+        <v>4.639000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5976</v>
@@ -1546,10 +1546,10 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3735000000000002</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0983</v>
+        <v>-0.7249</v>
       </c>
       <c r="U14" t="n">
         <v>0.7248999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>D. MUTAF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0084</v>
+        <v>1.619</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4428</v>
+        <v>1.7098</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4344</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3469</v>
+        <v>1.331</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1357</v>
+        <v>-0.1512</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2112</v>
+        <v>1.4822</v>
       </c>
       <c r="J15" t="n">
-        <v>0.79</v>
+        <v>1.7098</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0539</v>
+        <v>0.0168</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7361</v>
+        <v>1.693</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1369</v>
+        <v>-0.3788</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1896</v>
+        <v>-0.168</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.9473</v>
+        <v>-0.2108</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8191</v>
+        <v>0.056</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5806</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2385</v>
+        <v>0.056</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MUTAF</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5854</v>
+        <v>1.2163</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7098</v>
+        <v>2.6171</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1245</v>
+        <v>-1.4008</v>
       </c>
       <c r="G16" t="n">
-        <v>1.331</v>
+        <v>-1.3469</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1512</v>
+        <v>-0.1357</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4822</v>
+        <v>-1.2112</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7098</v>
+        <v>0.79</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0168</v>
+        <v>0.0539</v>
       </c>
       <c r="L16" t="n">
-        <v>1.693</v>
+        <v>0.7361</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3788</v>
+        <v>-2.1369</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.168</v>
+        <v>-0.1896</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2108</v>
+        <v>-1.9473</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0224</v>
+        <v>1.0271</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.7549</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0224</v>
+        <v>0.2721</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7518</v>
+        <v>0.7044</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5666</v>
+        <v>0.5634</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1852</v>
+        <v>0.141</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0914</v>
+        <v>0.5989</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4779</v>
+        <v>-0.1776</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5693</v>
+        <v>0.7764</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9673</v>
+        <v>2.7215</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7625999999999999</v>
+        <v>0.2556</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7298</v>
+        <v>2.4659</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8759</v>
+        <v>-2.1226</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7153</v>
+        <v>-0.4331</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1605</v>
+        <v>-1.6895</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2661</v>
+        <v>-0.6831</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9911</v>
+        <v>-0.5344</v>
       </c>
       <c r="U17" t="n">
-        <v>0.275</v>
+        <v>-0.1487</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2019</v>
+        <v>0.4372</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4835</v>
+        <v>0.0948</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6854</v>
+        <v>0.3424</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2999</v>
+        <v>0.0914</v>
       </c>
       <c r="H18" t="n">
-        <v>0.611</v>
+        <v>-1.4779</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3111</v>
+        <v>1.5693</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9002</v>
+        <v>0.9673</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7897999999999999</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>1.7298</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6004</v>
+        <v>-0.8759</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1788</v>
+        <v>-0.7153</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4216</v>
+        <v>-0.1605</v>
       </c>
       <c r="P18" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3659</v>
+        <v>0.9515</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>0.5192</v>
       </c>
       <c r="U18" t="n">
-        <v>0.59</v>
+        <v>0.4323</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2665</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2096</v>
+        <v>-0.3656</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.476</v>
+        <v>0.4502</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5989</v>
+        <v>0.2999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1776</v>
+        <v>0.611</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7764</v>
+        <v>-0.3111</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7215</v>
+        <v>0.9002</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2556</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4659</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1226</v>
+        <v>-0.6004</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4331</v>
+        <v>-0.1788</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6895</v>
+        <v>-0.4216</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.654</v>
+        <v>0.2486</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8883</v>
+        <v>-0.1061</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7657</v>
+        <v>0.3547</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.2824</v>
       </c>
       <c r="E20" t="n">
         <v>0.1707</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1037</v>
+        <v>-0.4531</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6242</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7547</v>
+        <v>-0.1041</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1687</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.586</v>
+        <v>0.0646</v>
       </c>
       <c r="V20" t="n">
         <v>1.214</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3551</v>
+        <v>-1.3071</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7634</v>
+        <v>-0.8818</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4083</v>
+        <v>-0.4253</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-3.4782</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5533</v>
+        <v>-1.5809</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-1.8973</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7024</v>
+        <v>-2.109</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6288</v>
+        <v>-0.215</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-1.894</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7111</v>
+        <v>-1.3692</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0755</v>
+        <v>-1.366</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.63</v>
+        <v>0.1711</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5895</v>
+        <v>-0.1491</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0404</v>
+        <v>0.3203</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2525</v>
+        <v>1.6083</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6979</v>
+        <v>-1.3995</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0418</v>
+        <v>-1.7634</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.656</v>
+        <v>0.3639</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1226</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5579</v>
+        <v>0.5533</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4354</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>5.9493</v>
+        <v>0.7024</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3272</v>
+        <v>0.6288</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6222</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8268</v>
+        <v>-0.7111</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7692</v>
+        <v>-0.0755</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0576</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.4071</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.3349</v>
+        <v>-1.6237</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4134</v>
+        <v>-0.6743</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6563</v>
+        <v>-0.5895</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2429</v>
+        <v>-0.0848</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9869</v>
+        <v>-1.4055</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4715</v>
+        <v>0.1941</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5154</v>
+        <v>-1.5996</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4782</v>
+        <v>3.1226</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5809</v>
+        <v>4.5579</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8973</v>
+        <v>-1.4354</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.109</v>
+        <v>5.9493</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.215</v>
+        <v>5.3272</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.894</v>
+        <v>0.6222</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3692</v>
+        <v>-2.8268</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.366</v>
+        <v>-0.7692</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0033</v>
+        <v>-2.0576</v>
       </c>
       <c r="P23" t="n">
+        <v>-4.4071</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-5.3349</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1598</v>
-      </c>
       <c r="S23" t="n">
-        <v>-0.5087</v>
+        <v>-0.121</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7389</v>
+        <v>-0.4204</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2302</v>
+        <v>0.2994</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6131</v>
+        <v>-2.7031</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2864</v>
+        <v>-0.1854</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8995</v>
+        <v>-2.5177</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4517</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0552</v>
+        <v>0.9651</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1483</v>
+        <v>0.6765</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0931</v>
+        <v>0.2886</v>
       </c>
       <c r="V24" t="n">
         <v>-3.2166</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6416</v>
+        <v>-4.3378</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.083</v>
+        <v>-3.6112</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5585</v>
+        <v>-0.7266</v>
       </c>
       <c r="G26" t="n">
         <v>-4.2897</v>
@@ -2482,13 +2482,13 @@
         <v>0.9278</v>
       </c>
       <c r="S26" t="n">
-        <v>0.112</v>
+        <v>0.4158</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5816</v>
+        <v>-0.1098</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6937</v>
+        <v>0.5256</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.7658</v>
+        <v>-10.1931</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.738500000000001</v>
+        <v>-1.7387</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.027</v>
+        <v>-8.4544</v>
       </c>
       <c r="G27" t="n">
         <v>-6.680400000000001</v>
@@ -2533,7 +2533,7 @@
         <v>-8.414999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>9.8307</v>
+        <v>9.830699999999997</v>
       </c>
       <c r="K27" t="n">
         <v>7.422700000000001</v>
@@ -2545,13 +2545,13 @@
         <v>-16.5113</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.688199999999999</v>
+        <v>-5.6882</v>
       </c>
       <c r="O27" t="n">
         <v>-10.8231</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.638999999999998</v>
+        <v>-4.638999999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.2368</v>
@@ -2560,19 +2560,19 @@
         <v>11.5978</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3732999999999997</v>
+        <v>1.9461</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7247999999999998</v>
+        <v>-0.7249000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.0983</v>
+        <v>2.6709</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.8196999999999997</v>
+        <v>-0.8197000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>5.3921</v>
+        <v>5.392099999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-6.2118</v>
